--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487806_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487806_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7482</v>
+        <v>2.6857</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6473</v>
+        <v>4.8197</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.8991</v>
+        <v>-2.134</v>
       </c>
       <c r="G2" t="n">
         <v>2.2946</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0757</v>
+        <v>-0.1381</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3295</v>
+        <v>-0.1571</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2539</v>
+        <v>0.019</v>
       </c>
       <c r="V2" t="n">
         <v>2.4023</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0502</v>
+        <v>1.1704</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5326</v>
+        <v>2.7703</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4824</v>
+        <v>-1.5999</v>
       </c>
       <c r="G3" t="n">
         <v>-0.3233</v>
@@ -688,13 +688,13 @@
         <v>0.4162</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2603</v>
+        <v>0.3805</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.1691</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3289</v>
+        <v>0.2114</v>
       </c>
       <c r="V3" t="n">
         <v>0.697</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1912</v>
+        <v>0.4834</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3305</v>
+        <v>2.0166</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5217000000000001</v>
+        <v>-1.5332</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4307</v>
+        <v>0.5819</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7761</v>
+        <v>-0.5178</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3454</v>
+        <v>1.0997</v>
       </c>
       <c r="J4" t="n">
-        <v>0.092</v>
+        <v>1.7822</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1431</v>
+        <v>0.1151</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2351</v>
+        <v>1.6671</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5227000000000001</v>
+        <v>-1.2004</v>
       </c>
       <c r="N4" t="n">
         <v>-0.6329</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1102</v>
+        <v>-0.5674</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7724</v>
+        <v>0.299</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6524</v>
+        <v>0.2343</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.12</v>
+        <v>0.0646</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3538</v>
+        <v>-0.8137</v>
       </c>
       <c r="W4" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1238</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1642</v>
+        <v>0.4349</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8442</v>
+        <v>-0.1162</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.68</v>
+        <v>0.5511</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5819</v>
+        <v>-0.4307</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5178</v>
+        <v>-0.7761</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0997</v>
+        <v>0.3454</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7822</v>
+        <v>0.092</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1151</v>
+        <v>-0.1431</v>
       </c>
       <c r="L5" t="n">
-        <v>1.6671</v>
+        <v>0.2351</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2004</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="N5" t="n">
         <v>-0.6329</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5674</v>
+        <v>0.1102</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0202</v>
+        <v>-0.5288</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0619</v>
+        <v>-0.4381</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0822</v>
+        <v>-0.0906</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8137</v>
+        <v>0.3538</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8137</v>
+        <v>0.1238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3736</v>
+        <v>-1.4297</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8309</v>
+        <v>0.9077</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2045</v>
+        <v>-2.3374</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8165</v>
+        <v>0.4263</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.307</v>
+        <v>-0.8718</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5094</v>
+        <v>1.2981</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9718</v>
+        <v>1.6757</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9506</v>
+        <v>0.0959</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0212</v>
+        <v>1.5798</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7883</v>
+        <v>-1.2494</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2576</v>
+        <v>-0.9677</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.2817</v>
       </c>
       <c r="P6" t="n">
+        <v>-1.2487</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-2.0812</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-3.1218</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4025</v>
+        <v>-0.5614</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6458</v>
+        <v>-0.4381</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2433</v>
+        <v>-0.1233</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1215</v>
+        <v>-0.046</v>
       </c>
       <c r="W6" t="n">
-        <v>2.3351</v>
+        <v>1.7513</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2135</v>
+        <v>-1.7973</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8496</v>
+        <v>-1.7854</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6934</v>
+        <v>0.3604</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.543</v>
+        <v>-2.1458</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4263</v>
+        <v>-0.8165</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8718</v>
+        <v>-0.307</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2981</v>
+        <v>-0.5094</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6757</v>
+        <v>0.9718</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0959</v>
+        <v>0.9506</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5798</v>
+        <v>0.0212</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2494</v>
+        <v>-1.7883</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9677</v>
+        <v>-1.2576</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2817</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9812</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6524</v>
+        <v>0.1753</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3288</v>
+        <v>-0.1846</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.046</v>
+        <v>1.1215</v>
       </c>
       <c r="W7" t="n">
-        <v>1.7513</v>
+        <v>2.3351</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7973</v>
+        <v>-1.2135</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.4796</v>
+        <v>-2.1707</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6503</v>
+        <v>-0.3707</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8293</v>
+        <v>-1.7999</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4384</v>
@@ -1078,13 +1078,13 @@
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.76</v>
+        <v>-0.4511</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7177</v>
+        <v>-0.4381</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0424</v>
+        <v>-0.013</v>
       </c>
       <c r="V8" t="n">
         <v>0.9268999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6854</v>
+        <v>-2.8536</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1885</v>
+        <v>-0.0677</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8739</v>
+        <v>-2.7858</v>
       </c>
       <c r="G9" t="n">
         <v>-1.6019</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3569</v>
+        <v>0.1887</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2577</v>
+        <v>0.0014</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0992</v>
+        <v>0.1873</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3998</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1407</v>
+        <v>-3.3317</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2497</v>
+        <v>-1.4407</v>
       </c>
       <c r="F10" t="n">
         <v>-1.891</v>
@@ -1234,10 +1234,10 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7796</v>
+        <v>0.5886</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5153</v>
+        <v>0.3244</v>
       </c>
       <c r="U10" t="n">
         <v>0.2643</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.378299999999999</v>
+        <v>-9.3043</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8981</v>
+        <v>-4.6186</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4802</v>
+        <v>-4.6857</v>
       </c>
       <c r="G11" t="n">
         <v>-3.8387</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0339</v>
+        <v>0.108</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5219</v>
+        <v>-0.2424</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3504</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4518</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-16.7534</v>
+        <v>-16.101</v>
       </c>
       <c r="E12" t="n">
-        <v>3.608299999999999</v>
+        <v>4.260800000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.3617</v>
+        <v>-20.3616</v>
       </c>
       <c r="G12" t="n">
         <v>-7.6555</v>
@@ -1390,10 +1390,10 @@
         <v>6.243499999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7762999999999999</v>
+        <v>-0.1239</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4617</v>
+        <v>-0.8092999999999999</v>
       </c>
       <c r="U12" t="n">
         <v>0.6855</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4682</v>
+        <v>5.2498</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0343</v>
+        <v>3.9628</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4338</v>
+        <v>1.287</v>
       </c>
       <c r="G13" t="n">
         <v>2.186</v>
@@ -1468,13 +1468,13 @@
         <v>2.2893</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2533</v>
+        <v>0.0349</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0992</v>
+        <v>0.0277</v>
       </c>
       <c r="U13" t="n">
-        <v>0.154</v>
+        <v>0.0072</v>
       </c>
       <c r="V13" t="n">
         <v>1.9883</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.598</v>
+        <v>4.5536</v>
       </c>
       <c r="E14" t="n">
-        <v>4.595</v>
+        <v>5.3451</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.997</v>
+        <v>-0.7915</v>
       </c>
       <c r="G14" t="n">
         <v>5.6473</v>
@@ -1546,13 +1546,13 @@
         <v>2.4974</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3198</v>
+        <v>-0.3642</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0967</v>
+        <v>-0.3467</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2231</v>
+        <v>-0.0176</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9376</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. SAGNIA</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2664</v>
+        <v>3.2524</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9404</v>
+        <v>5.0221</v>
       </c>
       <c r="F15" t="n">
-        <v>0.326</v>
+        <v>-1.7697</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2482</v>
+        <v>1.9964</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5135</v>
+        <v>4.1216</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2653</v>
+        <v>-2.1251</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8565</v>
+        <v>2.9885</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6606</v>
+        <v>3.7993</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1959</v>
+        <v>-0.8107</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6083</v>
+        <v>-0.9921</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.147</v>
+        <v>0.3223</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4613</v>
+        <v>-1.3144</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.6649</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3649</v>
+        <v>-0.0551</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8945</v>
+        <v>-0.3233</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4704</v>
+        <v>0.2682</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3467</v>
+        <v>-0.3538</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>2.565</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5767</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>A. RODRIGUEZ AGUILAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.404</v>
+        <v>2.2983</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3792</v>
+        <v>2.6659</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9752</v>
+        <v>-0.3676</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9964</v>
+        <v>0.5971</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1216</v>
+        <v>-0.2258</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.1251</v>
+        <v>0.823</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9885</v>
+        <v>1.626</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7993</v>
+        <v>-0.1195</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8107</v>
+        <v>1.7455</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9921</v>
+        <v>-1.0289</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3223</v>
+        <v>-0.1063</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.3144</v>
+        <v>-0.9225</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9036</v>
+        <v>-0.2632</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9663</v>
+        <v>-0.1276</v>
       </c>
       <c r="U16" t="n">
-        <v>0.06270000000000001</v>
+        <v>-0.1357</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3538</v>
+        <v>-0.1168</v>
       </c>
       <c r="W16" t="n">
-        <v>2.565</v>
+        <v>1.1675</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.9188</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7987</v>
+        <v>2.0511</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7862</v>
+        <v>2.2148</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0125</v>
+        <v>-0.1637</v>
       </c>
       <c r="G17" t="n">
         <v>1.7483</v>
@@ -1780,13 +1780,13 @@
         <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.779</v>
+        <v>-0.5265</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9134</v>
+        <v>-0.4848</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1344</v>
+        <v>-0.0417</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0437</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ AGUILAR</t>
+          <t>N. SAGNIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5673</v>
+        <v>2.029</v>
       </c>
       <c r="E18" t="n">
-        <v>2.023</v>
+        <v>1.7617</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4557</v>
+        <v>0.2673</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5971</v>
+        <v>1.2482</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2258</v>
+        <v>1.5135</v>
       </c>
       <c r="I18" t="n">
-        <v>0.823</v>
+        <v>-0.2653</v>
       </c>
       <c r="J18" t="n">
-        <v>1.626</v>
+        <v>1.8565</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1195</v>
+        <v>1.6606</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7455</v>
+        <v>0.1959</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0289</v>
+        <v>-0.6083</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1063</v>
+        <v>-0.147</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9225</v>
+        <v>-0.4613</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0812</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0812</v>
+        <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9943</v>
+        <v>1.1275</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7705</v>
+        <v>0.7158</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2237</v>
+        <v>0.4117</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1168</v>
+        <v>-0.3467</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2843</v>
+        <v>-0.5767</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3412</v>
+        <v>1.1166</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1475</v>
+        <v>1.0403</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1937</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6087</v>
@@ -1936,13 +1936,13 @@
         <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9499</v>
+        <v>0.7252999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3353</v>
+        <v>0.2281</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6146</v>
+        <v>0.4972</v>
       </c>
       <c r="V19" t="n">
         <v>1.1675</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4013</v>
+        <v>0.7814</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4957</v>
+        <v>0.8172</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0944</v>
+        <v>-0.0357</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1949</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7033</v>
+        <v>-0.3231</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4567</v>
+        <v>-0.1352</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V20" t="n">
         <v>1.0508</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7341</v>
+        <v>-0.5785</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1777</v>
+        <v>0.392</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9118000000000001</v>
+        <v>-0.9705</v>
       </c>
       <c r="G21" t="n">
         <v>-0.035</v>
@@ -2092,13 +2092,13 @@
         <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0391</v>
+        <v>0.1164</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3262</v>
+        <v>-0.1119</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2871</v>
+        <v>0.2284</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2843</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3575</v>
+        <v>-4.0005</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2173</v>
+        <v>-2.8603</v>
       </c>
       <c r="F22" t="n">
         <v>-1.1402</v>
@@ -2170,10 +2170,10 @@
         <v>1.0406</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9473</v>
+        <v>0.3043</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5153</v>
+        <v>-0.1276</v>
       </c>
       <c r="U22" t="n">
         <v>0.4319</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>16.7535</v>
+        <v>16.7532</v>
       </c>
       <c r="E23" t="n">
-        <v>20.36170000000001</v>
+        <v>20.3616</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6083</v>
+        <v>-3.608300000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>7.655499999999998</v>
+        <v>7.6555</v>
       </c>
       <c r="H23" t="n">
         <v>11.0438</v>
@@ -2248,10 +2248,10 @@
         <v>15.609</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7763000000000001</v>
+        <v>0.7763</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6854999999999999</v>
+        <v>-0.6855</v>
       </c>
       <c r="U23" t="n">
         <v>1.4617</v>
